--- a/product_surveys/031_form_field_structure_survey--product_surveys.xlsx
+++ b/product_surveys/031_form_field_structure_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>job_level</t>
+          <t>job_level_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Job Level</t>
+          <t>Job Level 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_filling_experience</t>
+          <t>form_filling_experience_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Form Filling Experience</t>
+          <t>Form Filling Experience 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>most_frequent_form_type</t>
+          <t>most_frequent_form_type_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Most Frequent Form Type</t>
+          <t>Most Frequent Form Type 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>time_spent_in_form</t>
+          <t>time_spent_in_form_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Time Spent in Form</t>
+          <t>Time Spent In Form 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>date_of_last_form_submission</t>
+          <t>date_of_last_form_submission_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Date of Last Form Submission</t>
+          <t>Date Of Last Form Submission 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'small_business',_'value':_'small_business'}</t>
+          <t>small_business</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Small Business', 'value': 'small_business'}</t>
+          <t>Small Business</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'medium_business',_'value':_'medium_business'}</t>
+          <t>medium_business</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Medium Business', 'value': 'medium_business'}</t>
+          <t>Medium Business</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'large_business',_'value':_'large_business'}</t>
+          <t>large_business</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Large Business', 'value': 'large_business'}</t>
+          <t>Large Business</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'enterprise',_'value':_'enterprise'}</t>
+          <t>enterprise</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Enterprise', 'value': 'enterprise'}</t>
+          <t>Enterprise</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing', 'value': 'marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'finance',_'value':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Finance', 'value': 'finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'operations',_'value':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Operations', 'value': 'operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'human_resources',_'value':_'human_resources'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Human Resources', 'value': 'human_resources'}</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'entry_level',_'value':_'entry_level'}</t>
+          <t>entry_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Entry Level', 'value': 'entry_level'}</t>
+          <t>Entry Level</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'mid_level',_'value':_'mid_level'}</t>
+          <t>mid_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Mid Level', 'value': 'mid_level'}</t>
+          <t>Mid Level</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'senior_level',_'value':_'senior_level'}</t>
+          <t>senior_level</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Senior Level', 'value': 'senior_level'}</t>
+          <t>Senior Level</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_a_year',_'value':_'less_than_a_year'}</t>
+          <t>less_than_a_year</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Less than a year', 'value': 'less_than_a_year'}</t>
+          <t>Less than a year</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_years',_'value':_'one_to_two_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '1-2 years', 'value': 'one_to_two_years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_2_years',_'value':_'more_than_two_years'}</t>
+          <t>more_than_2_years</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'More than 2 years', 'value': 'more_than_two_years'}</t>
+          <t>More than 2 years</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'single_field',_'value':_'single_field'}</t>
+          <t>single_field</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Single Field', 'value': 'single_field'}</t>
+          <t>Single Field</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'multi_field',_'value':_'multi_field'}</t>
+          <t>multi_field</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Multi Field', 'value': 'multi_field'}</t>
+          <t>Multi Field</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
